--- a/backend/excel/leads.xlsx
+++ b/backend/excel/leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,6 +639,302 @@
       <c r="P3" t="inlineStr">
         <is>
           <t>2026-10-07 16:01:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>lead_1b86953f637d</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tcs</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>tcs@gmail.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>08884949844</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>cmp_34d1f236a61f</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Cold Call</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Contacted</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>emp_3dbe82c7aa1d</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>linkin</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>call the company</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:42:45</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:42:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>lead_3b826568ba91</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tcs</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>tcs@gmail.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>08884949844</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>cmp_34d1f236a61f</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cold Call</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Contacted</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>emp_3dbe82c7aa1d</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>linkin</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>call the company</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:42:50</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:42:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>lead_a081fb0cf492</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>tcs</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>tcs@gmail.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>08884949844</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>cmp_34d1f236a61f</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Cold Call</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Contacted</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>emp_3dbe82c7aa1d</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>linkin</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>call the company</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:43:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>lead_2f8d3eba4432</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>tcs</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>tcs@gmail.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>08884949844</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>cmp_34d1f236a61f</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Cold Call</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Contacted</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>emp_3dbe82c7aa1d</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>linkin</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>call the company</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:43:05</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:54:20</t>
         </is>
       </c>
     </row>

--- a/backend/excel/leads.xlsx
+++ b/backend/excel/leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,150 +495,6 @@
       <c r="P1" t="inlineStr">
         <is>
           <t>updated_at</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>lead_40d2ac2ba106</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Loghan .K.J</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>loghankj@gmail.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5448565565445</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>cmp_f5234d6be069</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Contacted</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>emp_3dbe82c7aa1d</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>website desiging</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>complete the work</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2026-10-07 15:42:36</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2026-10-07 16:28:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>lead_28a475ed3c75</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>hcl</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>hcl@gaml.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>54485655654450</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>cmp_96f0e46740a8</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Qualified</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>emp_fac939ae2286</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>complete and update your satuts</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2026-10-07 16:01:44</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2026-10-07 16:01:44</t>
         </is>
       </c>
     </row>
